--- a/mp257/v0.1/LPDDR4_Memory_length_equalization_in_mm_for_STM32MP25xxAK (14x14)_Template.xlsx
+++ b/mp257/v0.1/LPDDR4_Memory_length_equalization_in_mm_for_STM32MP25xxAK (14x14)_Template.xlsx
@@ -8,10 +8,10 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="LPDDR4" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Classified as UnClassified" sheetId="3" state="hidden" r:id="rId4"/>
-    <sheet name="xl_DCF_History" sheetId="4" state="hidden" r:id="rId5"/>
+    <sheet name="Info" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="LPDDR4" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Classified as UnClassified" sheetId="3" state="hidden" r:id="rId5"/>
+    <sheet name="xl_DCF_History" sheetId="4" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="CLOCK_A_LENGHTS" vbProcedure="false">LPDDR4!$G$7:$G$8</definedName>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="205">
   <si>
     <t xml:space="preserve">LPDDR4_memory_length_equalization_in_mm_for_STM32MP25xxAK</t>
   </si>
@@ -93,7 +93,7 @@
     <t xml:space="preserve">A0</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CKE0_A</t>
+    <t xml:space="preserve">DDR_CKE</t>
   </si>
   <si>
     <t xml:space="preserve">value</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">A1</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CKE1_A</t>
+    <t xml:space="preserve">NA</t>
   </si>
   <si>
     <t xml:space="preserve">outside the limits</t>
@@ -114,13 +114,13 @@
     <t xml:space="preserve">A2</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA0_A</t>
+    <t xml:space="preserve">DDR_CSN</t>
   </si>
   <si>
     <t xml:space="preserve">A3</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA1_A</t>
+    <t xml:space="preserve">DDR_ODT</t>
   </si>
   <si>
     <t xml:space="preserve">Color in column G shows shortest (green) and longest (red) lenghts in  the group.</t>
@@ -141,28 +141,22 @@
     <t xml:space="preserve">A6</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CS0_A</t>
-  </si>
-  <si>
     <t xml:space="preserve">A7</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CS1_A</t>
-  </si>
-  <si>
     <t xml:space="preserve">NA  = Not Applicable</t>
   </si>
   <si>
     <t xml:space="preserve">A8</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA2_A</t>
+    <t xml:space="preserve">DDR_A3</t>
   </si>
   <si>
     <t xml:space="preserve">A9</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA3_A</t>
+    <t xml:space="preserve">DDR_CASN</t>
   </si>
   <si>
     <t xml:space="preserve">Modifiable cell</t>
@@ -171,109 +165,121 @@
     <t xml:space="preserve">A10</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA4_A</t>
+    <t xml:space="preserve">DDR_RASN</t>
   </si>
   <si>
     <t xml:space="preserve">A11</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA5_A</t>
+    <t xml:space="preserve">DDR_A11</t>
   </si>
   <si>
     <t xml:space="preserve">A12</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CKE0_B</t>
+    <t xml:space="preserve">DDR_A0</t>
   </si>
   <si>
     <t xml:space="preserve">A13</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CKE1_B</t>
+    <t xml:space="preserve">DDR_A6</t>
   </si>
   <si>
     <t xml:space="preserve">A14</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA0_B</t>
+    <t xml:space="preserve">DDR_A8</t>
   </si>
   <si>
     <t xml:space="preserve">A15</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA1_B</t>
+    <t xml:space="preserve">DDR_A2</t>
   </si>
   <si>
     <t xml:space="preserve">A16</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CLK_B_P</t>
+    <t xml:space="preserve">DDR_BA0</t>
   </si>
   <si>
     <t xml:space="preserve">A17</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CLK_B_N</t>
+    <t xml:space="preserve">DDR_A10</t>
   </si>
   <si>
     <t xml:space="preserve">A18</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CS0_B</t>
-  </si>
-  <si>
     <t xml:space="preserve">A19</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CS1_B</t>
-  </si>
-  <si>
     <t xml:space="preserve">A20</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA2_B</t>
+    <t xml:space="preserve">DDR_A4</t>
   </si>
   <si>
     <t xml:space="preserve">A21</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA3_B</t>
+    <t xml:space="preserve">DDR_BG0</t>
   </si>
   <si>
     <t xml:space="preserve">A22</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA4_B</t>
+    <t xml:space="preserve">DDR_ACTN</t>
   </si>
   <si>
     <t xml:space="preserve">A23</t>
   </si>
   <si>
-    <t xml:space="preserve">DDR_CA5_B</t>
+    <t xml:space="preserve">DDR_WEN</t>
   </si>
   <si>
     <t xml:space="preserve">A25</t>
   </si>
   <si>
-    <t xml:space="preserve">NA</t>
+    <t xml:space="preserve">DDR_A5</t>
   </si>
   <si>
     <t xml:space="preserve">A26</t>
   </si>
   <si>
+    <t xml:space="preserve">DDR_A9</t>
+  </si>
+  <si>
     <t xml:space="preserve">A27</t>
   </si>
   <si>
+    <t xml:space="preserve">DDR_BA1</t>
+  </si>
+  <si>
     <t xml:space="preserve">A28</t>
   </si>
   <si>
+    <t xml:space="preserve">DDR_A13</t>
+  </si>
+  <si>
     <t xml:space="preserve">A29</t>
   </si>
   <si>
+    <t xml:space="preserve">DDR_A1</t>
+  </si>
+  <si>
     <t xml:space="preserve">A30</t>
   </si>
   <si>
+    <t xml:space="preserve">DDR_A7</t>
+  </si>
+  <si>
     <t xml:space="preserve">A31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDR_A12</t>
   </si>
   <si>
     <t xml:space="preserve">DELTA WITH ((DQSn_P+DQSn_N)/2)
@@ -771,12 +777,14 @@
       <color rgb="FF000000"/>
       <name val="PingFang SC"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1040,24 +1048,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="75">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1065,7 +1073,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -1073,71 +1081,67 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1145,31 +1149,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1177,19 +1181,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1197,27 +1201,27 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1225,23 +1229,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1249,23 +1253,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1273,43 +1277,31 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1317,39 +1309,43 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1362,29 +1358,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="20">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF39A9DC"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="17">
     <dxf>
       <font>
         <b val="1"/>
@@ -1412,14 +1386,13 @@
         <color rgb="FF000000"/>
         <sz val="11"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </dxf>
     <dxf>
       <font>
         <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1435,7 +1408,7 @@
         <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1508,7 +1481,7 @@
         <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1524,7 +1497,7 @@
         <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1540,7 +1513,7 @@
         <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1556,7 +1529,7 @@
         <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1569,7 +1542,7 @@
         <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1585,7 +1558,7 @@
         <b val="1"/>
         <i val="0"/>
         <strike val="0"/>
-        <color rgb="00FFFFFF"/>
+        <color rgb="FFFFFFFF"/>
       </font>
       <fill>
         <patternFill>
@@ -1668,9 +1641,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>2653560</xdr:colOff>
+      <xdr:colOff>2653200</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>33120</xdr:rowOff>
+      <xdr:rowOff>48600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1684,7 +1657,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="190440"/>
-          <a:ext cx="2653560" cy="2003040"/>
+          <a:ext cx="2653200" cy="2002680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1699,6 +1672,112 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1711,14 +1790,14 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="54.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="11.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="10.58"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="9" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" s="1" customFormat="true" ht="35.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" s="1" customFormat="true" ht="33.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1843,7 +1922,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L85"/>
-  <sheetFormatPr defaultColWidth="11.41796875" defaultRowHeight="17.7" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="17.7" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="9" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="18"/>
@@ -1857,9 +1936,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="10" width="7.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="10" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="10" width="88.84"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="13" style="10" width="11.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="19" min="13" style="10" width="11.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="10" width="15.41"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="10" width="11.42"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="21" style="10" width="11.43"/>
   </cols>
   <sheetData>
     <row r="1" s="12" customFormat="true" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1899,820 +1978,815 @@
       <c r="I2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="19"/>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="17"/>
+      <c r="K2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="20"/>
+      <c r="L2" s="19"/>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="24" t="n">
+      <c r="D3" s="23" t="n">
         <v>3.249</v>
       </c>
-      <c r="E3" s="19"/>
-      <c r="F3" s="25" t="n">
-        <v>29</v>
-      </c>
-      <c r="G3" s="26" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>32.249</v>
-      </c>
-      <c r="H3" s="27" t="n">
+      <c r="E3" s="17"/>
+      <c r="F3" s="24" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G3" s="25" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>30.749</v>
+      </c>
+      <c r="H3" s="26" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>-0.324999999999996</v>
-      </c>
-      <c r="I3" s="28"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="29" t="s">
+        <v>1.925</v>
+      </c>
+      <c r="I3" s="27"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="30" t="s">
+      <c r="L3" s="29" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21"/>
-      <c r="B4" s="29" t="s">
+      <c r="A4" s="20"/>
+      <c r="B4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="32" t="n">
+      <c r="D4" s="31" t="n">
         <v>7.455</v>
       </c>
-      <c r="E4" s="19"/>
-      <c r="F4" s="33" t="n">
-        <v>26</v>
-      </c>
-      <c r="G4" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>33.455</v>
-      </c>
-      <c r="H4" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>0.881</v>
-      </c>
-      <c r="I4" s="28"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21"/>
-      <c r="B5" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="32" t="n">
-        <v>4.177</v>
-      </c>
-      <c r="E5" s="19"/>
-      <c r="F5" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G5" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>33.177</v>
-      </c>
-      <c r="H5" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>0.603000000000002</v>
-      </c>
-      <c r="I5" s="28"/>
-      <c r="J5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21"/>
-      <c r="B6" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="32" t="n">
-        <v>2.883</v>
-      </c>
-      <c r="E6" s="19"/>
-      <c r="F6" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G6" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>31.883</v>
-      </c>
-      <c r="H6" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>-0.690999999999999</v>
-      </c>
-      <c r="I6" s="28"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="39"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21"/>
-      <c r="B7" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="32" t="n">
-        <v>3.668</v>
-      </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G7" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>32.668</v>
-      </c>
-      <c r="H7" s="40"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-    </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21"/>
-      <c r="B8" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="32" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="E8" s="19"/>
-      <c r="F8" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G8" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>32.48</v>
-      </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="28"/>
-      <c r="J8" s="19"/>
-    </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21"/>
-      <c r="B9" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="32" t="n">
-        <v>6.416</v>
-      </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G9" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>35.416</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>2.842</v>
-      </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21"/>
-      <c r="B10" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="32" t="n">
-        <v>8.297</v>
-      </c>
-      <c r="E10" s="19"/>
-      <c r="F10" s="33" t="n">
-        <v>25</v>
-      </c>
-      <c r="G10" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>33.297</v>
-      </c>
-      <c r="H10" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>0.722999999999999</v>
-      </c>
-      <c r="I10" s="28"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="L10" s="41"/>
-    </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21"/>
-      <c r="B11" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="32" t="n">
-        <v>3.998</v>
-      </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G11" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>32.998</v>
-      </c>
-      <c r="H11" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>0.424</v>
-      </c>
-      <c r="I11" s="28"/>
-      <c r="J11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21"/>
-      <c r="B12" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="32" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G12" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>31.87</v>
-      </c>
-      <c r="H12" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>-0.703999999999997</v>
-      </c>
-      <c r="I12" s="28"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="42" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12" s="42"/>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21"/>
-      <c r="B13" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="32" t="n">
-        <v>2.803</v>
-      </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G13" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>31.803</v>
-      </c>
-      <c r="H13" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>-0.770999999999997</v>
-      </c>
-      <c r="I13" s="28"/>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21"/>
-      <c r="B14" s="43" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="44" t="n">
-        <v>3.232</v>
-      </c>
-      <c r="E14" s="19"/>
-      <c r="F14" s="45" t="n">
-        <v>29</v>
-      </c>
-      <c r="G14" s="46" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>32.232</v>
-      </c>
-      <c r="H14" s="47" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>-0.341999999999999</v>
-      </c>
-      <c r="I14" s="28"/>
-    </row>
-    <row r="15" customFormat="false" ht="15.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21"/>
-      <c r="B15" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="50" t="n">
-        <v>5.642</v>
-      </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="51" t="n">
-        <v>28</v>
-      </c>
-      <c r="G15" s="52" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>33.642</v>
-      </c>
-      <c r="H15" s="53" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>27.7005</v>
-      </c>
-      <c r="I15" s="28"/>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21"/>
-      <c r="B16" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="32" t="n">
-        <v>5.788</v>
-      </c>
-      <c r="E16" s="19"/>
-      <c r="F16" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G16" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>34.788</v>
-      </c>
-      <c r="H16" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>28.8465</v>
-      </c>
-      <c r="I16" s="28"/>
-    </row>
-    <row r="17" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21"/>
-      <c r="B17" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="32" t="n">
-        <v>4.525</v>
-      </c>
-      <c r="E17" s="19"/>
-      <c r="F17" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G17" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>33.525</v>
-      </c>
-      <c r="H17" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>27.5835</v>
-      </c>
-      <c r="I17" s="28"/>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
-      <c r="B18" s="29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="32" t="n">
-        <v>2.989</v>
-      </c>
-      <c r="E18" s="19"/>
-      <c r="F18" s="33" t="n">
-        <v>29</v>
-      </c>
-      <c r="G18" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>31.989</v>
-      </c>
-      <c r="H18" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>26.0475</v>
-      </c>
-      <c r="I18" s="28"/>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21"/>
-      <c r="B19" s="29" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="32" t="n">
-        <v>5.447</v>
-      </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>5.447</v>
-      </c>
-      <c r="H19" s="40"/>
-      <c r="I19" s="35" t="n">
-        <f aca="false">AVERAGEA(CLOCK_A_LENGHTS)-AVERAGEA(CLOCK_B_LENGHTS)</f>
-        <v>26.6325</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21"/>
-      <c r="B20" s="29" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20" s="32" t="n">
-        <v>6.436</v>
-      </c>
-      <c r="E20" s="19"/>
-      <c r="F20" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>6.436</v>
-      </c>
-      <c r="H20" s="40"/>
-      <c r="I20" s="35"/>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21"/>
-      <c r="B21" s="29" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="32" t="n">
-        <v>6.249</v>
-      </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>6.249</v>
-      </c>
-      <c r="H21" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>0.3075</v>
-      </c>
-      <c r="I21" s="54"/>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21"/>
-      <c r="B22" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="32" t="n">
-        <v>2.614</v>
-      </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>2.614</v>
-      </c>
-      <c r="H22" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>-3.3275</v>
-      </c>
-      <c r="I22" s="54"/>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21"/>
-      <c r="B23" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="32" t="n">
-        <v>3.763</v>
-      </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>3.763</v>
-      </c>
-      <c r="H23" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>-2.1785</v>
-      </c>
-      <c r="I23" s="54"/>
-    </row>
-    <row r="24" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21"/>
-      <c r="B24" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="32" t="n">
-        <v>4.491</v>
-      </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>4.491</v>
-      </c>
-      <c r="H24" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>-1.4505</v>
-      </c>
-      <c r="I24" s="54"/>
-    </row>
-    <row r="25" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21"/>
-      <c r="B25" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="32" t="n">
-        <v>4.868</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>4.868</v>
-      </c>
-      <c r="H25" s="35" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>-1.0735</v>
-      </c>
-      <c r="I25" s="54"/>
-    </row>
-    <row r="26" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21"/>
-      <c r="B26" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="56" t="n">
-        <v>8.075</v>
-      </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="58" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>8.075</v>
-      </c>
-      <c r="H26" s="59" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>2.1335</v>
-      </c>
-      <c r="I26" s="54"/>
-    </row>
-    <row r="27" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="24" t="n">
-        <v>5.302</v>
-      </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" s="26" t="str">
+      <c r="E4" s="17"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="33" t="str">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>NA</v>
       </c>
-      <c r="H27" s="27" t="str">
+      <c r="H4" s="34" t="str">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
         <v>NA</v>
       </c>
-      <c r="I27" s="54"/>
-    </row>
-    <row r="28" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21"/>
-      <c r="B28" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="32" t="n">
-        <v>8.368</v>
-      </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="G28" s="34" t="str">
+      <c r="I4" s="27"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20"/>
+      <c r="B5" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="31" t="n">
+        <v>4.177</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="G5" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.177</v>
+      </c>
+      <c r="H5" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-0.646999999999999</v>
+      </c>
+      <c r="I5" s="27"/>
+      <c r="J5" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="20"/>
+      <c r="B6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>2.883</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="32" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G6" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.783</v>
+      </c>
+      <c r="H6" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-0.0410000000000004</v>
+      </c>
+      <c r="I6" s="27"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" s="38"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="20"/>
+      <c r="B7" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>3.668</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.668</v>
+      </c>
+      <c r="H7" s="39"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="20"/>
+      <c r="B8" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G8" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.98</v>
+      </c>
+      <c r="H8" s="39"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="17"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="20"/>
+      <c r="B9" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>6.416</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="33" t="str">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>NA</v>
       </c>
-      <c r="H28" s="35" t="str">
+      <c r="H9" s="34" t="str">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
         <v>NA</v>
       </c>
-      <c r="I28" s="54"/>
-    </row>
-    <row r="29" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21"/>
-      <c r="B29" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="32" t="n">
-        <v>7.661</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="G29" s="34" t="str">
+      <c r="I9" s="27"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="20"/>
+      <c r="B10" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="31" t="n">
+        <v>8.297</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="33" t="str">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>NA</v>
       </c>
-      <c r="H29" s="35" t="str">
+      <c r="H10" s="34" t="str">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
         <v>NA</v>
       </c>
-      <c r="I29" s="54"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="L10" s="40"/>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="20"/>
+      <c r="B11" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>3.998</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="32" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>26.598</v>
+      </c>
+      <c r="H11" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-2.226</v>
+      </c>
+      <c r="I11" s="27"/>
+      <c r="J11" s="17"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="20"/>
+      <c r="B12" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="32" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G12" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>25.67</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-3.154</v>
+      </c>
+      <c r="I12" s="27"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="L12" s="41"/>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="20"/>
+      <c r="B13" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="31" t="n">
+        <v>2.803</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="32" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="G13" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>26.103</v>
+      </c>
+      <c r="H13" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-2.721</v>
+      </c>
+      <c r="I13" s="27"/>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="20"/>
+      <c r="B14" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="43" t="n">
+        <v>3.232</v>
+      </c>
+      <c r="E14" s="17"/>
+      <c r="F14" s="44" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="G14" s="45" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>26.032</v>
+      </c>
+      <c r="H14" s="46" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-2.792</v>
+      </c>
+      <c r="I14" s="27"/>
+    </row>
+    <row r="15" customFormat="false" ht="15.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="20"/>
+      <c r="B15" s="47" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>5.642</v>
+      </c>
+      <c r="E15" s="17"/>
+      <c r="F15" s="50" t="n">
+        <v>23</v>
+      </c>
+      <c r="G15" s="51" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.642</v>
+      </c>
+      <c r="H15" s="52" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>1.3005</v>
+      </c>
+      <c r="I15" s="27"/>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20"/>
+      <c r="B16" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>5.788</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="G16" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.788</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>1.4465</v>
+      </c>
+      <c r="I16" s="27"/>
+    </row>
+    <row r="17" customFormat="false" ht="17.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20"/>
+      <c r="B17" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>4.525</v>
+      </c>
+      <c r="E17" s="17"/>
+      <c r="F17" s="32" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G17" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>30.425</v>
+      </c>
+      <c r="H17" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>3.0835</v>
+      </c>
+      <c r="I17" s="27"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="20"/>
+      <c r="B18" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>2.989</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="G18" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.989</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>1.6475</v>
+      </c>
+      <c r="I18" s="27"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="20"/>
+      <c r="B19" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>5.447</v>
+      </c>
+      <c r="E19" s="17"/>
+      <c r="F19" s="32" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G19" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>25.947</v>
+      </c>
+      <c r="H19" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>-1.3945</v>
+      </c>
+      <c r="I19" s="34" t="n">
+        <f aca="false">AVERAGEA(CLOCK_A_LENGHTS)-AVERAGEA(CLOCK_B_LENGHTS)</f>
+        <v>1.4825</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="20"/>
+      <c r="B20" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>6.436</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="32" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="G20" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.736</v>
+      </c>
+      <c r="H20" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>1.3945</v>
+      </c>
+      <c r="I20" s="34"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="20"/>
+      <c r="B21" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>6.249</v>
+      </c>
+      <c r="E21" s="17"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="33" t="str">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>NA</v>
+      </c>
+      <c r="H21" s="34" t="str">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>NA</v>
+      </c>
+      <c r="I21" s="53"/>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="20"/>
+      <c r="B22" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>2.614</v>
+      </c>
+      <c r="E22" s="17"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="33" t="str">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>NA</v>
+      </c>
+      <c r="H22" s="34" t="str">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>NA</v>
+      </c>
+      <c r="I22" s="53"/>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20"/>
+      <c r="B23" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="31" t="n">
+        <v>3.763</v>
+      </c>
+      <c r="E23" s="17"/>
+      <c r="F23" s="32" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G23" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>27.863</v>
+      </c>
+      <c r="H23" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>0.5215</v>
+      </c>
+      <c r="I23" s="53"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="20"/>
+      <c r="B24" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>4.491</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="32" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="G24" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>27.891</v>
+      </c>
+      <c r="H24" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>0.549499999999998</v>
+      </c>
+      <c r="I24" s="53"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20"/>
+      <c r="B25" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="31" t="n">
+        <v>4.868</v>
+      </c>
+      <c r="E25" s="17"/>
+      <c r="F25" s="32" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G25" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>26.568</v>
+      </c>
+      <c r="H25" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>-0.773500000000002</v>
+      </c>
+      <c r="I25" s="53"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="20"/>
+      <c r="B26" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="55" t="n">
+        <v>8.075</v>
+      </c>
+      <c r="E26" s="17"/>
+      <c r="F26" s="56" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="G26" s="57" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.675</v>
+      </c>
+      <c r="H26" s="58" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_B_LENGHTS))</f>
+        <v>1.3335</v>
+      </c>
+      <c r="I26" s="53"/>
+    </row>
+    <row r="27" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="20"/>
+      <c r="B27" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="23" t="n">
+        <v>5.302</v>
+      </c>
+      <c r="E27" s="17"/>
+      <c r="F27" s="56" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G27" s="57" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>25.802</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-3.022</v>
+      </c>
+      <c r="I27" s="53"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="20"/>
+      <c r="B28" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="D28" s="31" t="n">
+        <v>8.368</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="56" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G28" s="57" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>25.568</v>
+      </c>
+      <c r="H28" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-3.256</v>
+      </c>
+      <c r="I28" s="53"/>
+    </row>
+    <row r="29" customFormat="false" ht="15.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>7.661</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="56" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G29" s="57" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>26.161</v>
+      </c>
+      <c r="H29" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-2.663</v>
+      </c>
+      <c r="I29" s="53"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21"/>
-      <c r="B30" s="29" t="s">
+      <c r="A30" s="20"/>
+      <c r="B30" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C30" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>9.257</v>
+      </c>
+      <c r="E30" s="17"/>
+      <c r="F30" s="56" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="G30" s="57" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>26.457</v>
+      </c>
+      <c r="H30" s="34" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
+        <v>-2.367</v>
+      </c>
+      <c r="I30" s="53"/>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="20"/>
+      <c r="B31" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" s="32" t="n">
-        <v>9.257</v>
-      </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="G30" s="34" t="str">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>NA</v>
-      </c>
-      <c r="H30" s="35" t="str">
+      <c r="C31" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="31" t="n">
+        <v>7.158</v>
+      </c>
+      <c r="E31" s="17"/>
+      <c r="F31" s="56" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G31" s="57" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>26.258</v>
+      </c>
+      <c r="H31" s="34" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>NA</v>
-      </c>
-      <c r="I30" s="54"/>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21"/>
-      <c r="B31" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="32" t="n">
-        <v>7.158</v>
-      </c>
-      <c r="E31" s="19"/>
-      <c r="F31" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="G31" s="34" t="str">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>NA</v>
-      </c>
-      <c r="H31" s="35" t="str">
+        <v>-2.566</v>
+      </c>
+      <c r="I31" s="53"/>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="20"/>
+      <c r="B32" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>6.124</v>
+      </c>
+      <c r="E32" s="17"/>
+      <c r="F32" s="56" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="G32" s="57" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>25.324</v>
+      </c>
+      <c r="H32" s="34" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>NA</v>
-      </c>
-      <c r="I31" s="54"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21"/>
-      <c r="B32" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="D32" s="32" t="n">
-        <v>6.124</v>
-      </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="61" t="s">
-        <v>72</v>
-      </c>
-      <c r="G32" s="34" t="str">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>NA</v>
-      </c>
-      <c r="H32" s="35" t="str">
+        <v>-3.5</v>
+      </c>
+      <c r="I32" s="53"/>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="20"/>
+      <c r="B33" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="43" t="n">
+        <v>7.004</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="56" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="G33" s="57" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>28.504</v>
+      </c>
+      <c r="H33" s="46" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>NA</v>
-      </c>
-      <c r="I32" s="54"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21"/>
-      <c r="B33" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="C33" s="62" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="44" t="n">
-        <v>7.004</v>
-      </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="G33" s="46" t="str">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>NA</v>
-      </c>
-      <c r="H33" s="47" t="str">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>NA</v>
-      </c>
-      <c r="I33" s="54"/>
-    </row>
-    <row r="37" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="38" customFormat="false" ht="42.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>-0.32</v>
+      </c>
+      <c r="I33" s="53"/>
+    </row>
+    <row r="38" customFormat="false" ht="34.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="13"/>
-      <c r="B38" s="64" t="s">
+      <c r="B38" s="60" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="15" t="s">
@@ -2729,1114 +2803,1113 @@
         <v>12</v>
       </c>
       <c r="H38" s="15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" s="66" t="s">
-        <v>82</v>
-      </c>
-      <c r="C39" s="38" t="s">
+      <c r="A39" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="24" t="n">
+      <c r="B39" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="23" t="n">
         <v>5.226</v>
       </c>
-      <c r="E39" s="19"/>
-      <c r="F39" s="25" t="n">
+      <c r="E39" s="17"/>
+      <c r="F39" s="24" t="n">
         <v>16.39</v>
       </c>
-      <c r="G39" s="26" t="n">
+      <c r="G39" s="25" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>21.616</v>
       </c>
-      <c r="H39" s="26" t="n">
+      <c r="H39" s="25" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
         <v>0.109000000000002</v>
       </c>
-      <c r="I39" s="28"/>
-    </row>
-    <row r="40" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="65"/>
-      <c r="B40" s="67" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="68" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="32" t="n">
+      <c r="I39" s="27"/>
+    </row>
+    <row r="40" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="61"/>
+      <c r="B40" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="31" t="n">
         <v>5.425</v>
       </c>
-      <c r="E40" s="19"/>
-      <c r="F40" s="33" t="n">
+      <c r="E40" s="17"/>
+      <c r="F40" s="32" t="n">
         <v>16.4</v>
       </c>
-      <c r="G40" s="34" t="n">
+      <c r="G40" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>21.825</v>
       </c>
-      <c r="H40" s="34" t="n">
+      <c r="H40" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
         <v>0.318000000000001</v>
       </c>
-      <c r="I40" s="28"/>
-    </row>
-    <row r="41" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="65"/>
-      <c r="B41" s="67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C41" s="68" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" s="32" t="n">
+      <c r="I40" s="27"/>
+    </row>
+    <row r="41" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="61"/>
+      <c r="B41" s="63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="64" t="s">
+        <v>89</v>
+      </c>
+      <c r="D41" s="31" t="n">
         <v>5.994</v>
       </c>
-      <c r="E41" s="19"/>
-      <c r="F41" s="33" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="G41" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>21.694</v>
-      </c>
-      <c r="H41" s="34" t="n">
+      <c r="E41" s="17"/>
+      <c r="F41" s="32" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="G41" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>22.394</v>
+      </c>
+      <c r="H41" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
-        <v>0.187000000000001</v>
-      </c>
-      <c r="I41" s="28"/>
-    </row>
-    <row r="42" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="65"/>
-      <c r="B42" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="68" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="32" t="n">
+        <v>0.887000000000001</v>
+      </c>
+      <c r="I41" s="27"/>
+    </row>
+    <row r="42" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="61"/>
+      <c r="B42" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="64" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="31" t="n">
         <v>5.98</v>
       </c>
-      <c r="E42" s="19"/>
-      <c r="F42" s="33" t="n">
+      <c r="E42" s="17"/>
+      <c r="F42" s="32" t="n">
         <v>16.4</v>
       </c>
-      <c r="G42" s="34" t="n">
+      <c r="G42" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>22.38</v>
       </c>
-      <c r="H42" s="34" t="n">
+      <c r="H42" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
         <v>0.873000000000001</v>
       </c>
-      <c r="I42" s="28"/>
-    </row>
-    <row r="43" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="65"/>
-      <c r="B43" s="67" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="68" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="32" t="n">
+      <c r="I42" s="27"/>
+    </row>
+    <row r="43" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="61"/>
+      <c r="B43" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" s="64" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="31" t="n">
         <v>4.037</v>
       </c>
-      <c r="E43" s="19"/>
-      <c r="F43" s="33" t="n">
+      <c r="E43" s="17"/>
+      <c r="F43" s="32" t="n">
         <v>16.4</v>
       </c>
-      <c r="G43" s="34" t="n">
+      <c r="G43" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>20.437</v>
       </c>
-      <c r="H43" s="34" t="n">
+      <c r="H43" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
         <v>-1.07</v>
       </c>
-      <c r="I43" s="28"/>
-    </row>
-    <row r="44" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="65"/>
-      <c r="B44" s="67" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="68" t="s">
-        <v>93</v>
-      </c>
-      <c r="D44" s="32" t="n">
+      <c r="I43" s="27"/>
+    </row>
+    <row r="44" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="61"/>
+      <c r="B44" s="63" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="31" t="n">
         <v>5.028</v>
       </c>
-      <c r="E44" s="19"/>
-      <c r="F44" s="33" t="n">
+      <c r="E44" s="17"/>
+      <c r="F44" s="32" t="n">
         <v>16.4</v>
       </c>
-      <c r="G44" s="34" t="n">
+      <c r="G44" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>21.428</v>
       </c>
-      <c r="H44" s="34" t="n">
+      <c r="H44" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
         <v>-0.0790000000000006</v>
       </c>
-      <c r="I44" s="28"/>
-    </row>
-    <row r="45" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="65"/>
-      <c r="B45" s="67" t="s">
-        <v>94</v>
-      </c>
-      <c r="C45" s="68" t="s">
-        <v>95</v>
-      </c>
-      <c r="D45" s="32" t="n">
+      <c r="I44" s="27"/>
+    </row>
+    <row r="45" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="61"/>
+      <c r="B45" s="63" t="s">
+        <v>96</v>
+      </c>
+      <c r="C45" s="64" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" s="31" t="n">
         <v>4.856</v>
       </c>
-      <c r="E45" s="19"/>
-      <c r="F45" s="33" t="n">
+      <c r="E45" s="17"/>
+      <c r="F45" s="32" t="n">
         <v>16.4</v>
       </c>
-      <c r="G45" s="34" t="n">
+      <c r="G45" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>21.256</v>
       </c>
-      <c r="H45" s="34" t="n">
+      <c r="H45" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
         <v>-0.250999999999998</v>
       </c>
-      <c r="I45" s="28"/>
-    </row>
-    <row r="46" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="65"/>
-      <c r="B46" s="67" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="68" t="s">
-        <v>97</v>
-      </c>
-      <c r="D46" s="32" t="n">
+      <c r="I45" s="27"/>
+    </row>
+    <row r="46" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="61"/>
+      <c r="B46" s="63" t="s">
+        <v>98</v>
+      </c>
+      <c r="C46" s="64" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" s="31" t="n">
         <v>3.987</v>
       </c>
-      <c r="E46" s="19"/>
-      <c r="F46" s="33" t="n">
+      <c r="E46" s="17"/>
+      <c r="F46" s="32" t="n">
         <v>16.4</v>
       </c>
-      <c r="G46" s="34" t="n">
+      <c r="G46" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>20.387</v>
       </c>
-      <c r="H46" s="34" t="n">
+      <c r="H46" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
         <v>-1.12</v>
       </c>
-      <c r="I46" s="28"/>
-    </row>
-    <row r="47" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="65"/>
-      <c r="B47" s="67" t="s">
-        <v>98</v>
-      </c>
-      <c r="C47" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" s="32" t="n">
+      <c r="I46" s="27"/>
+    </row>
+    <row r="47" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="61"/>
+      <c r="B47" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="C47" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="31" t="n">
         <v>6.086</v>
       </c>
-      <c r="E47" s="19"/>
-      <c r="F47" s="33" t="n">
+      <c r="E47" s="17"/>
+      <c r="F47" s="32" t="n">
         <v>16.5</v>
       </c>
-      <c r="G47" s="34" t="n">
+      <c r="G47" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>22.586</v>
       </c>
-      <c r="H47" s="34" t="n">
+      <c r="H47" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_A_LENGTHS))</f>
         <v>1.079</v>
       </c>
-      <c r="I47" s="28"/>
-    </row>
-    <row r="48" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="65"/>
-      <c r="B48" s="67" t="s">
-        <v>100</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="D48" s="32" t="n">
+      <c r="I47" s="27"/>
+    </row>
+    <row r="48" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="61"/>
+      <c r="B48" s="63" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="31" t="n">
         <v>4.964</v>
       </c>
-      <c r="E48" s="19"/>
-      <c r="F48" s="33" t="n">
+      <c r="E48" s="17"/>
+      <c r="F48" s="32" t="n">
         <v>16.4</v>
       </c>
-      <c r="G48" s="34" t="n">
+      <c r="G48" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>21.364</v>
       </c>
-      <c r="H48" s="69"/>
-      <c r="I48" s="47" t="n">
+      <c r="H48" s="65"/>
+      <c r="I48" s="46" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",AVERAGEA(DQS0_A_LENGTHS)-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>-11.067</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="65"/>
-      <c r="B49" s="70" t="s">
-        <v>102</v>
-      </c>
-      <c r="C49" s="62" t="s">
-        <v>103</v>
-      </c>
-      <c r="D49" s="44" t="n">
+        <v>-7.317</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="61"/>
+      <c r="B49" s="66" t="s">
+        <v>104</v>
+      </c>
+      <c r="C49" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="D49" s="43" t="n">
         <v>5.05</v>
       </c>
-      <c r="E49" s="19"/>
-      <c r="F49" s="45" t="n">
+      <c r="E49" s="17"/>
+      <c r="F49" s="44" t="n">
         <v>16.6</v>
       </c>
-      <c r="G49" s="46" t="n">
+      <c r="G49" s="45" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>21.65</v>
       </c>
-      <c r="H49" s="69"/>
-      <c r="I49" s="47"/>
+      <c r="H49" s="65"/>
+      <c r="I49" s="46"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="65" t="s">
-        <v>104</v>
-      </c>
-      <c r="B50" s="66" t="s">
-        <v>105</v>
-      </c>
-      <c r="C50" s="38" t="s">
+      <c r="A50" s="61" t="s">
         <v>106</v>
       </c>
-      <c r="D50" s="24" t="n">
+      <c r="B50" s="62" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="D50" s="23" t="n">
         <v>5.649</v>
       </c>
-      <c r="E50" s="19"/>
-      <c r="F50" s="25" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G50" s="26" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>42.549</v>
-      </c>
-      <c r="H50" s="26" t="n">
+      <c r="E50" s="17"/>
+      <c r="F50" s="24" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="G50" s="25" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>39.749</v>
+      </c>
+      <c r="H50" s="25" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-1.1535</v>
-      </c>
-      <c r="I50" s="28"/>
-    </row>
-    <row r="51" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="65"/>
-      <c r="B51" s="67" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="68" t="s">
-        <v>108</v>
-      </c>
-      <c r="D51" s="32" t="n">
+        <v>-0.803499999999993</v>
+      </c>
+      <c r="I50" s="27"/>
+    </row>
+    <row r="51" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="61"/>
+      <c r="B51" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="C51" s="64" t="s">
+        <v>110</v>
+      </c>
+      <c r="D51" s="31" t="n">
         <v>4.817</v>
       </c>
-      <c r="E51" s="19"/>
-      <c r="F51" s="33" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G51" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>41.717</v>
-      </c>
-      <c r="H51" s="34" t="n">
+      <c r="E51" s="17"/>
+      <c r="F51" s="32" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="G51" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>39.317</v>
+      </c>
+      <c r="H51" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-1.9855</v>
-      </c>
-      <c r="I51" s="28"/>
-    </row>
-    <row r="52" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="65"/>
-      <c r="B52" s="67" t="s">
-        <v>109</v>
-      </c>
-      <c r="C52" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="D52" s="32" t="n">
+        <v>-1.23549999999999</v>
+      </c>
+      <c r="I51" s="27"/>
+    </row>
+    <row r="52" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="61"/>
+      <c r="B52" s="63" t="s">
+        <v>111</v>
+      </c>
+      <c r="C52" s="64" t="s">
+        <v>112</v>
+      </c>
+      <c r="D52" s="31" t="n">
         <v>5.73</v>
       </c>
-      <c r="E52" s="19"/>
-      <c r="F52" s="33" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G52" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>42.63</v>
-      </c>
-      <c r="H52" s="34" t="n">
+      <c r="E52" s="17"/>
+      <c r="F52" s="32" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G52" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>40.83</v>
+      </c>
+      <c r="H52" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-1.07250000000001</v>
-      </c>
-      <c r="I52" s="28"/>
-    </row>
-    <row r="53" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="65"/>
-      <c r="B53" s="67" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53" s="68" t="s">
-        <v>112</v>
-      </c>
-      <c r="D53" s="32" t="n">
+        <v>0.277500000000003</v>
+      </c>
+      <c r="I52" s="27"/>
+    </row>
+    <row r="53" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="61"/>
+      <c r="B53" s="63" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" s="64" t="s">
+        <v>114</v>
+      </c>
+      <c r="D53" s="31" t="n">
         <v>5.346</v>
       </c>
-      <c r="E53" s="19"/>
-      <c r="F53" s="33" t="n">
-        <v>35.9</v>
-      </c>
-      <c r="G53" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>41.246</v>
-      </c>
-      <c r="H53" s="34" t="n">
+      <c r="E53" s="17"/>
+      <c r="F53" s="32" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="G53" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>41.646</v>
+      </c>
+      <c r="H53" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-2.45650000000001</v>
-      </c>
-      <c r="I53" s="28"/>
-    </row>
-    <row r="54" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="65"/>
-      <c r="B54" s="67" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="68" t="s">
-        <v>114</v>
-      </c>
-      <c r="D54" s="32" t="n">
+        <v>1.09350000000001</v>
+      </c>
+      <c r="I53" s="27"/>
+    </row>
+    <row r="54" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="61"/>
+      <c r="B54" s="63" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="64" t="s">
+        <v>116</v>
+      </c>
+      <c r="D54" s="31" t="n">
         <v>4.796</v>
       </c>
-      <c r="E54" s="19"/>
-      <c r="F54" s="33" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G54" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>41.696</v>
-      </c>
-      <c r="H54" s="34" t="n">
+      <c r="E54" s="17"/>
+      <c r="F54" s="32" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="G54" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>40.496</v>
+      </c>
+      <c r="H54" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-2.0065</v>
-      </c>
-      <c r="I54" s="28"/>
-    </row>
-    <row r="55" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="65"/>
-      <c r="B55" s="67" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" s="68" t="s">
-        <v>116</v>
-      </c>
-      <c r="D55" s="32" t="n">
+        <v>-0.0564999999999927</v>
+      </c>
+      <c r="I54" s="27"/>
+    </row>
+    <row r="55" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="61"/>
+      <c r="B55" s="63" t="s">
+        <v>117</v>
+      </c>
+      <c r="C55" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" s="31" t="n">
         <v>5.085</v>
       </c>
-      <c r="E55" s="19"/>
-      <c r="F55" s="33" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G55" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>41.985</v>
-      </c>
-      <c r="H55" s="34" t="n">
+      <c r="E55" s="17"/>
+      <c r="F55" s="32" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="G55" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>40.185</v>
+      </c>
+      <c r="H55" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-1.7175</v>
-      </c>
-      <c r="I55" s="28"/>
-    </row>
-    <row r="56" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="65"/>
-      <c r="B56" s="67" t="s">
-        <v>117</v>
-      </c>
-      <c r="C56" s="68" t="s">
-        <v>118</v>
-      </c>
-      <c r="D56" s="32" t="n">
+        <v>-0.367499999999993</v>
+      </c>
+      <c r="I55" s="27"/>
+    </row>
+    <row r="56" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="61"/>
+      <c r="B56" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="D56" s="31" t="n">
         <v>4.416</v>
       </c>
-      <c r="E56" s="19"/>
-      <c r="F56" s="33" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G56" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>41.316</v>
-      </c>
-      <c r="H56" s="34" t="n">
+      <c r="E56" s="17"/>
+      <c r="F56" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="G56" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>41.416</v>
+      </c>
+      <c r="H56" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-2.3865</v>
-      </c>
-      <c r="I56" s="28"/>
-    </row>
-    <row r="57" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="65"/>
-      <c r="B57" s="67" t="s">
-        <v>119</v>
-      </c>
-      <c r="C57" s="68" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" s="32" t="n">
+        <v>0.863500000000002</v>
+      </c>
+      <c r="I56" s="27"/>
+    </row>
+    <row r="57" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="61"/>
+      <c r="B57" s="63" t="s">
+        <v>121</v>
+      </c>
+      <c r="C57" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="D57" s="31" t="n">
         <v>5.227</v>
       </c>
-      <c r="E57" s="19"/>
-      <c r="F57" s="33" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G57" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>42.127</v>
-      </c>
-      <c r="H57" s="34" t="n">
+      <c r="E57" s="17"/>
+      <c r="F57" s="32" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G57" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>39.527</v>
+      </c>
+      <c r="H57" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-1.57550000000001</v>
-      </c>
-      <c r="I57" s="28"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="65"/>
-      <c r="B58" s="67" t="s">
-        <v>121</v>
-      </c>
-      <c r="C58" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D58" s="32" t="n">
+        <v>-1.02549999999999</v>
+      </c>
+      <c r="I57" s="27"/>
+    </row>
+    <row r="58" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="61"/>
+      <c r="B58" s="63" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="D58" s="31" t="n">
         <v>5.205</v>
       </c>
-      <c r="E58" s="19"/>
-      <c r="F58" s="33" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G58" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>42.105</v>
-      </c>
-      <c r="H58" s="34" t="n">
+      <c r="E58" s="17"/>
+      <c r="F58" s="32" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="G58" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>40.805</v>
+      </c>
+      <c r="H58" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_A_LENGTHS))</f>
-        <v>-1.5975</v>
-      </c>
-      <c r="I58" s="28"/>
-    </row>
-    <row r="59" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="65"/>
-      <c r="B59" s="67" t="s">
-        <v>123</v>
-      </c>
-      <c r="C59" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="D59" s="32" t="n">
+        <v>0.252500000000005</v>
+      </c>
+      <c r="I58" s="27"/>
+    </row>
+    <row r="59" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="61"/>
+      <c r="B59" s="63" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D59" s="31" t="n">
         <v>6.717</v>
       </c>
-      <c r="E59" s="19"/>
-      <c r="F59" s="33" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G59" s="34" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>43.617</v>
-      </c>
-      <c r="H59" s="69"/>
-      <c r="I59" s="47" t="n">
+      <c r="E59" s="17"/>
+      <c r="F59" s="32" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G59" s="33" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>40.517</v>
+      </c>
+      <c r="H59" s="65"/>
+      <c r="I59" s="46" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",AVERAGEA(DQS1_A_LENGTHS)-AVERAGEA(CLOCK_A_LENGHTS))</f>
-        <v>11.1285</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="65"/>
-      <c r="B60" s="70" t="s">
-        <v>125</v>
-      </c>
-      <c r="C60" s="62" t="s">
-        <v>126</v>
-      </c>
-      <c r="D60" s="44" t="n">
+        <v>11.7285</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="61"/>
+      <c r="B60" s="66" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="D60" s="43" t="n">
         <v>6.888</v>
       </c>
-      <c r="E60" s="19"/>
-      <c r="F60" s="45" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="G60" s="46" t="n">
-        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
-        <v>43.788</v>
-      </c>
-      <c r="H60" s="69"/>
-      <c r="I60" s="47"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="44" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="G60" s="45" t="n">
+        <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
+        <v>40.588</v>
+      </c>
+      <c r="H60" s="65"/>
+      <c r="I60" s="46"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="71" t="s">
-        <v>127</v>
-      </c>
-      <c r="B61" s="66" t="s">
-        <v>128</v>
-      </c>
-      <c r="C61" s="38" t="s">
+      <c r="A61" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="D61" s="24" t="n">
+      <c r="B61" s="62" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="D61" s="23" t="n">
         <v>4.573</v>
       </c>
-      <c r="E61" s="19"/>
-      <c r="F61" s="25" t="n">
+      <c r="E61" s="17"/>
+      <c r="F61" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="26" t="n">
+      <c r="G61" s="25" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.573</v>
       </c>
-      <c r="H61" s="26" t="n">
+      <c r="H61" s="25" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>-0.770999999999999</v>
       </c>
-      <c r="I61" s="28"/>
-    </row>
-    <row r="62" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="71"/>
-      <c r="B62" s="67" t="s">
-        <v>130</v>
-      </c>
-      <c r="C62" s="68" t="s">
-        <v>131</v>
-      </c>
-      <c r="D62" s="32" t="n">
+      <c r="I61" s="27"/>
+    </row>
+    <row r="62" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="67"/>
+      <c r="B62" s="63" t="s">
+        <v>132</v>
+      </c>
+      <c r="C62" s="64" t="s">
+        <v>133</v>
+      </c>
+      <c r="D62" s="31" t="n">
         <v>5.346</v>
       </c>
-      <c r="E62" s="19"/>
-      <c r="F62" s="33" t="n">
+      <c r="E62" s="17"/>
+      <c r="F62" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="34" t="n">
+      <c r="G62" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>5.346</v>
       </c>
-      <c r="H62" s="34" t="n">
+      <c r="H62" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>0.00200000000000067</v>
       </c>
-      <c r="I62" s="28"/>
-    </row>
-    <row r="63" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="71"/>
-      <c r="B63" s="67" t="s">
-        <v>132</v>
-      </c>
-      <c r="C63" s="68" t="s">
-        <v>133</v>
-      </c>
-      <c r="D63" s="32" t="n">
+      <c r="I62" s="27"/>
+    </row>
+    <row r="63" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="67"/>
+      <c r="B63" s="63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="D63" s="31" t="n">
         <v>5.006</v>
       </c>
-      <c r="E63" s="19"/>
-      <c r="F63" s="33" t="n">
+      <c r="E63" s="17"/>
+      <c r="F63" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="34" t="n">
+      <c r="G63" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>5.006</v>
       </c>
-      <c r="H63" s="34" t="n">
+      <c r="H63" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>-0.337999999999999</v>
       </c>
-      <c r="I63" s="28"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="71"/>
-      <c r="B64" s="67" t="s">
-        <v>134</v>
-      </c>
-      <c r="C64" s="68" t="s">
-        <v>135</v>
-      </c>
-      <c r="D64" s="32" t="n">
+      <c r="I63" s="27"/>
+    </row>
+    <row r="64" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="67"/>
+      <c r="B64" s="63" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="64" t="s">
+        <v>137</v>
+      </c>
+      <c r="D64" s="31" t="n">
         <v>5.347</v>
       </c>
-      <c r="E64" s="19"/>
-      <c r="F64" s="33" t="n">
+      <c r="E64" s="17"/>
+      <c r="F64" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G64" s="34" t="n">
+      <c r="G64" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>5.347</v>
       </c>
-      <c r="H64" s="34" t="n">
+      <c r="H64" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>0.003000000000001</v>
       </c>
-      <c r="I64" s="28"/>
-    </row>
-    <row r="65" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="71"/>
-      <c r="B65" s="67" t="s">
-        <v>136</v>
-      </c>
-      <c r="C65" s="68" t="s">
-        <v>137</v>
-      </c>
-      <c r="D65" s="32" t="n">
+      <c r="I64" s="27"/>
+    </row>
+    <row r="65" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="67"/>
+      <c r="B65" s="63" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="64" t="s">
+        <v>139</v>
+      </c>
+      <c r="D65" s="31" t="n">
         <v>4.287</v>
       </c>
-      <c r="E65" s="19"/>
-      <c r="F65" s="33" t="n">
+      <c r="E65" s="17"/>
+      <c r="F65" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="34" t="n">
+      <c r="G65" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.287</v>
       </c>
-      <c r="H65" s="34" t="n">
+      <c r="H65" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>-1.057</v>
       </c>
-      <c r="I65" s="28"/>
-    </row>
-    <row r="66" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="71"/>
-      <c r="B66" s="67" t="s">
-        <v>138</v>
-      </c>
-      <c r="C66" s="68" t="s">
-        <v>139</v>
-      </c>
-      <c r="D66" s="32" t="n">
+      <c r="I65" s="27"/>
+    </row>
+    <row r="66" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="67"/>
+      <c r="B66" s="63" t="s">
+        <v>140</v>
+      </c>
+      <c r="C66" s="64" t="s">
+        <v>141</v>
+      </c>
+      <c r="D66" s="31" t="n">
         <v>4.652</v>
       </c>
-      <c r="E66" s="19"/>
-      <c r="F66" s="33" t="n">
+      <c r="E66" s="17"/>
+      <c r="F66" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="34" t="n">
+      <c r="G66" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.652</v>
       </c>
-      <c r="H66" s="34" t="n">
+      <c r="H66" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>-0.691999999999999</v>
       </c>
-      <c r="I66" s="28"/>
-    </row>
-    <row r="67" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="71"/>
-      <c r="B67" s="67" t="s">
-        <v>140</v>
-      </c>
-      <c r="C67" s="68" t="s">
-        <v>141</v>
-      </c>
-      <c r="D67" s="32" t="n">
+      <c r="I66" s="27"/>
+    </row>
+    <row r="67" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="67"/>
+      <c r="B67" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="64" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" s="31" t="n">
         <v>6.489</v>
       </c>
-      <c r="E67" s="19"/>
-      <c r="F67" s="33" t="n">
+      <c r="E67" s="17"/>
+      <c r="F67" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="34" t="n">
+      <c r="G67" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>6.489</v>
       </c>
-      <c r="H67" s="34" t="n">
+      <c r="H67" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>1.145</v>
       </c>
-      <c r="I67" s="28"/>
-    </row>
-    <row r="68" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="71"/>
-      <c r="B68" s="67" t="s">
-        <v>142</v>
-      </c>
-      <c r="C68" s="68" t="s">
-        <v>143</v>
-      </c>
-      <c r="D68" s="32" t="n">
+      <c r="I67" s="27"/>
+    </row>
+    <row r="68" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="67"/>
+      <c r="B68" s="63" t="s">
+        <v>144</v>
+      </c>
+      <c r="C68" s="64" t="s">
+        <v>145</v>
+      </c>
+      <c r="D68" s="31" t="n">
         <v>4.242</v>
       </c>
-      <c r="E68" s="19"/>
-      <c r="F68" s="33" t="n">
+      <c r="E68" s="17"/>
+      <c r="F68" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="34" t="n">
+      <c r="G68" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.242</v>
       </c>
-      <c r="H68" s="34" t="n">
+      <c r="H68" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>-1.102</v>
       </c>
-      <c r="I68" s="28"/>
-    </row>
-    <row r="69" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="71"/>
-      <c r="B69" s="67" t="s">
-        <v>144</v>
-      </c>
-      <c r="C69" s="31" t="s">
-        <v>145</v>
-      </c>
-      <c r="D69" s="32" t="n">
+      <c r="I68" s="27"/>
+    </row>
+    <row r="69" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="67"/>
+      <c r="B69" s="63" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="D69" s="31" t="n">
         <v>6.757</v>
       </c>
-      <c r="E69" s="19"/>
-      <c r="F69" s="33" t="n">
+      <c r="E69" s="17"/>
+      <c r="F69" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="34" t="n">
+      <c r="G69" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>6.757</v>
       </c>
-      <c r="H69" s="34" t="n">
+      <c r="H69" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS0_B_LENGTHS))</f>
         <v>1.413</v>
       </c>
-      <c r="I69" s="28"/>
-    </row>
-    <row r="70" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="71"/>
-      <c r="B70" s="67" t="s">
-        <v>146</v>
-      </c>
-      <c r="C70" s="31" t="s">
-        <v>147</v>
-      </c>
-      <c r="D70" s="32" t="n">
+      <c r="I69" s="27"/>
+    </row>
+    <row r="70" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="67"/>
+      <c r="B70" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="D70" s="31" t="n">
         <v>5.199</v>
       </c>
-      <c r="E70" s="19"/>
-      <c r="F70" s="33" t="n">
+      <c r="E70" s="17"/>
+      <c r="F70" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="34" t="n">
+      <c r="G70" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>5.199</v>
       </c>
-      <c r="H70" s="72"/>
-      <c r="I70" s="47" t="n">
+      <c r="H70" s="68"/>
+      <c r="I70" s="46" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",AVERAGEA(DQS0_B_LENGTHS)-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>-0.5975</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="71"/>
-      <c r="B71" s="73" t="s">
-        <v>148</v>
-      </c>
-      <c r="C71" s="74" t="s">
-        <v>149</v>
-      </c>
-      <c r="D71" s="56" t="n">
+        <v>-21.9975</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="67"/>
+      <c r="B71" s="69" t="s">
+        <v>150</v>
+      </c>
+      <c r="C71" s="70" t="s">
+        <v>151</v>
+      </c>
+      <c r="D71" s="55" t="n">
         <v>5.489</v>
       </c>
-      <c r="E71" s="19"/>
-      <c r="F71" s="45" t="n">
+      <c r="E71" s="17"/>
+      <c r="F71" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="58" t="n">
+      <c r="G71" s="57" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>5.489</v>
       </c>
-      <c r="H71" s="72"/>
-      <c r="I71" s="47"/>
+      <c r="H71" s="68"/>
+      <c r="I71" s="46"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="65" t="s">
-        <v>150</v>
-      </c>
-      <c r="B72" s="66" t="s">
-        <v>151</v>
-      </c>
-      <c r="C72" s="38" t="s">
+      <c r="A72" s="61" t="s">
         <v>152</v>
       </c>
-      <c r="D72" s="24" t="n">
+      <c r="B72" s="62" t="s">
+        <v>153</v>
+      </c>
+      <c r="C72" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="D72" s="23" t="n">
         <v>4.171</v>
       </c>
-      <c r="E72" s="19"/>
-      <c r="F72" s="25" t="n">
+      <c r="E72" s="17"/>
+      <c r="F72" s="24" t="n">
         <v>0</v>
       </c>
-      <c r="G72" s="26" t="n">
+      <c r="G72" s="25" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.171</v>
       </c>
-      <c r="H72" s="26" t="n">
+      <c r="H72" s="25" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>-0.632499999999999</v>
       </c>
-      <c r="I72" s="28"/>
-    </row>
-    <row r="73" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="65"/>
-      <c r="B73" s="67" t="s">
-        <v>153</v>
-      </c>
-      <c r="C73" s="68" t="s">
-        <v>154</v>
-      </c>
-      <c r="D73" s="32" t="n">
+      <c r="I72" s="27"/>
+    </row>
+    <row r="73" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="61"/>
+      <c r="B73" s="63" t="s">
+        <v>155</v>
+      </c>
+      <c r="C73" s="64" t="s">
+        <v>156</v>
+      </c>
+      <c r="D73" s="31" t="n">
         <v>4.186</v>
       </c>
-      <c r="E73" s="19"/>
-      <c r="F73" s="33" t="n">
+      <c r="E73" s="17"/>
+      <c r="F73" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G73" s="34" t="n">
+      <c r="G73" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.186</v>
       </c>
-      <c r="H73" s="34" t="n">
+      <c r="H73" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>-0.6175</v>
       </c>
-      <c r="I73" s="28"/>
-    </row>
-    <row r="74" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="65"/>
-      <c r="B74" s="67" t="s">
-        <v>155</v>
-      </c>
-      <c r="C74" s="68" t="s">
-        <v>156</v>
-      </c>
-      <c r="D74" s="32" t="n">
+      <c r="I73" s="27"/>
+    </row>
+    <row r="74" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="61"/>
+      <c r="B74" s="63" t="s">
+        <v>157</v>
+      </c>
+      <c r="C74" s="64" t="s">
+        <v>158</v>
+      </c>
+      <c r="D74" s="31" t="n">
         <v>4.313</v>
       </c>
-      <c r="E74" s="19"/>
-      <c r="F74" s="33" t="n">
+      <c r="E74" s="17"/>
+      <c r="F74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="34" t="n">
+      <c r="G74" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.313</v>
       </c>
-      <c r="H74" s="34" t="n">
+      <c r="H74" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>-0.4905</v>
       </c>
-      <c r="I74" s="28"/>
-    </row>
-    <row r="75" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="65"/>
-      <c r="B75" s="67" t="s">
-        <v>157</v>
-      </c>
-      <c r="C75" s="68" t="s">
-        <v>158</v>
-      </c>
-      <c r="D75" s="32" t="n">
+      <c r="I74" s="27"/>
+    </row>
+    <row r="75" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="61"/>
+      <c r="B75" s="63" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="64" t="s">
+        <v>160</v>
+      </c>
+      <c r="D75" s="31" t="n">
         <v>5.091</v>
       </c>
-      <c r="E75" s="19"/>
-      <c r="F75" s="33" t="n">
+      <c r="E75" s="17"/>
+      <c r="F75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="34" t="n">
+      <c r="G75" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>5.091</v>
       </c>
-      <c r="H75" s="34" t="n">
+      <c r="H75" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>0.287500000000001</v>
       </c>
-      <c r="I75" s="28"/>
-    </row>
-    <row r="76" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="65"/>
-      <c r="B76" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="C76" s="68" t="s">
-        <v>160</v>
-      </c>
-      <c r="D76" s="32" t="n">
+      <c r="I75" s="27"/>
+    </row>
+    <row r="76" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="61"/>
+      <c r="B76" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C76" s="64" t="s">
+        <v>162</v>
+      </c>
+      <c r="D76" s="31" t="n">
         <v>3.552</v>
       </c>
-      <c r="E76" s="19"/>
-      <c r="F76" s="33" t="n">
+      <c r="E76" s="17"/>
+      <c r="F76" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G76" s="34" t="n">
+      <c r="G76" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>3.552</v>
       </c>
-      <c r="H76" s="34" t="n">
+      <c r="H76" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>-1.2515</v>
       </c>
-      <c r="I76" s="28"/>
-    </row>
-    <row r="77" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="65"/>
-      <c r="B77" s="67" t="s">
-        <v>161</v>
-      </c>
-      <c r="C77" s="68" t="s">
-        <v>162</v>
-      </c>
-      <c r="D77" s="32" t="n">
+      <c r="I76" s="27"/>
+    </row>
+    <row r="77" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="61"/>
+      <c r="B77" s="63" t="s">
+        <v>163</v>
+      </c>
+      <c r="C77" s="64" t="s">
+        <v>164</v>
+      </c>
+      <c r="D77" s="31" t="n">
         <v>5.47</v>
       </c>
-      <c r="E77" s="19"/>
-      <c r="F77" s="33" t="n">
+      <c r="E77" s="17"/>
+      <c r="F77" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="34" t="n">
+      <c r="G77" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>5.47</v>
       </c>
-      <c r="H77" s="34" t="n">
+      <c r="H77" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>0.6665</v>
       </c>
-      <c r="I77" s="28"/>
-    </row>
-    <row r="78" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="65"/>
-      <c r="B78" s="67" t="s">
-        <v>163</v>
-      </c>
-      <c r="C78" s="68" t="s">
-        <v>164</v>
-      </c>
-      <c r="D78" s="32" t="n">
+      <c r="I77" s="27"/>
+    </row>
+    <row r="78" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="61"/>
+      <c r="B78" s="63" t="s">
+        <v>165</v>
+      </c>
+      <c r="C78" s="64" t="s">
+        <v>166</v>
+      </c>
+      <c r="D78" s="31" t="n">
         <v>4.969</v>
       </c>
-      <c r="E78" s="19"/>
-      <c r="F78" s="33" t="n">
+      <c r="E78" s="17"/>
+      <c r="F78" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G78" s="34" t="n">
+      <c r="G78" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.969</v>
       </c>
-      <c r="H78" s="34" t="n">
+      <c r="H78" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>0.165500000000001</v>
       </c>
-      <c r="I78" s="28"/>
-    </row>
-    <row r="79" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="65"/>
-      <c r="B79" s="67" t="s">
-        <v>165</v>
-      </c>
-      <c r="C79" s="68" t="s">
-        <v>166</v>
-      </c>
-      <c r="D79" s="32" t="n">
+      <c r="I78" s="27"/>
+    </row>
+    <row r="79" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="61"/>
+      <c r="B79" s="63" t="s">
+        <v>167</v>
+      </c>
+      <c r="C79" s="64" t="s">
+        <v>168</v>
+      </c>
+      <c r="D79" s="31" t="n">
         <v>5.165</v>
       </c>
-      <c r="E79" s="19"/>
-      <c r="F79" s="33" t="n">
+      <c r="E79" s="17"/>
+      <c r="F79" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G79" s="34" t="n">
+      <c r="G79" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>5.165</v>
       </c>
-      <c r="H79" s="34" t="n">
+      <c r="H79" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>0.3615</v>
       </c>
-      <c r="I79" s="28"/>
-    </row>
-    <row r="80" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="65"/>
-      <c r="B80" s="67" t="s">
-        <v>167</v>
-      </c>
-      <c r="C80" s="31" t="s">
-        <v>168</v>
-      </c>
-      <c r="D80" s="32" t="n">
+      <c r="I79" s="27"/>
+    </row>
+    <row r="80" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="61"/>
+      <c r="B80" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="C80" s="30" t="s">
+        <v>170</v>
+      </c>
+      <c r="D80" s="31" t="n">
         <v>4.841</v>
       </c>
-      <c r="E80" s="19"/>
-      <c r="F80" s="33" t="n">
+      <c r="E80" s="17"/>
+      <c r="F80" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G80" s="34" t="n">
+      <c r="G80" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.841</v>
       </c>
-      <c r="H80" s="34" t="n">
+      <c r="H80" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",G:G-AVERAGEA(DQS1_B_LENGTHS))</f>
         <v>0.0375000000000005</v>
       </c>
-      <c r="I80" s="28"/>
-    </row>
-    <row r="81" customFormat="false" ht="14.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="65"/>
-      <c r="B81" s="67" t="s">
-        <v>169</v>
-      </c>
-      <c r="C81" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="D81" s="32" t="n">
+      <c r="I80" s="27"/>
+    </row>
+    <row r="81" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="61"/>
+      <c r="B81" s="63" t="s">
+        <v>171</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D81" s="31" t="n">
         <v>4.976</v>
       </c>
-      <c r="E81" s="19"/>
-      <c r="F81" s="33" t="n">
+      <c r="E81" s="17"/>
+      <c r="F81" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="34" t="n">
+      <c r="G81" s="33" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.976</v>
       </c>
-      <c r="H81" s="69"/>
-      <c r="I81" s="47" t="n">
+      <c r="H81" s="65"/>
+      <c r="I81" s="46" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",AVERAGEA(DQS1_B_LENGTHS)-AVERAGEA(CLOCK_B_LENGHTS))</f>
-        <v>-1.138</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="65"/>
-      <c r="B82" s="70" t="s">
-        <v>171</v>
-      </c>
-      <c r="C82" s="62" t="s">
-        <v>172</v>
-      </c>
-      <c r="D82" s="44" t="n">
+        <v>-22.538</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="61"/>
+      <c r="B82" s="66" t="s">
+        <v>173</v>
+      </c>
+      <c r="C82" s="59" t="s">
+        <v>174</v>
+      </c>
+      <c r="D82" s="43" t="n">
         <v>4.631</v>
       </c>
-      <c r="E82" s="19"/>
-      <c r="F82" s="45" t="n">
+      <c r="E82" s="17"/>
+      <c r="F82" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="46" t="n">
+      <c r="G82" s="45" t="n">
         <f aca="false">IF(OR(NET_NAME="NA",F:F="NA"),"NA",PACKAGE_LENGTH+F:F)</f>
         <v>4.631</v>
       </c>
-      <c r="H82" s="69"/>
-      <c r="I82" s="47"/>
+      <c r="H82" s="65"/>
+      <c r="I82" s="46"/>
     </row>
     <row r="85" customFormat="false" ht="17.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F85" s="75"/>
+      <c r="F85" s="71"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" objects="true" scenarios="true"/>
-  <mergeCells count="26">
+  <mergeCells count="25">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="A3:A33"/>
@@ -3844,7 +3917,6 @@
     <mergeCell ref="K6:L7"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="K12:L12"/>
-    <mergeCell ref="H19:H20"/>
     <mergeCell ref="I19:I20"/>
     <mergeCell ref="I21:I33"/>
     <mergeCell ref="A39:A49"/>
@@ -3865,58 +3937,58 @@
     <mergeCell ref="I81:I82"/>
   </mergeCells>
   <conditionalFormatting sqref="A34:L1048576">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>CELL("protect",A34)=0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>NOT(ISNUMBER(A34))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19">
-    <cfRule type="cellIs" priority="5" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="cellIs" priority="5" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>-14.5</formula>
       <formula>14.5</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="cellIs" priority="6" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>-14.5</formula>
       <formula>14.5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I19 I2:I3 I21">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>CELL("protect",I2)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I3 I19 I21">
-    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>NOT(ISNUMBER(I2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:L33">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>CELL("protect",J2)=0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="11" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="cellIs" priority="11" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>NOT(ISNUMBER(J2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:L1 A2:H33">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>CELL("protect",A1)=0</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="cellIs" priority="14" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>"NA"</formula>
     </cfRule>
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>NOT(ISNUMBER(A1))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3969,21 +4041,21 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H39:H82">
-    <cfRule type="cellIs" priority="20" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="cellIs" priority="20" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>-1.42</formula>
       <formula>1.42</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="21" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="cellIs" priority="21" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>-1.42</formula>
       <formula>1.42</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48 I59 I70 I81">
-    <cfRule type="cellIs" priority="22" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="cellIs" priority="22" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>-12.07</formula>
       <formula>12.07</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="23" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="cellIs" priority="23" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>-12.07</formula>
       <formula>12.07</formula>
     </cfRule>
@@ -4001,11 +4073,11 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H33">
-    <cfRule type="cellIs" priority="25" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="cellIs" priority="25" operator="between" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>-3.55</formula>
       <formula>3.55</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="26" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="cellIs" priority="26" operator="notBetween" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>-3.55</formula>
       <formula>3.55</formula>
     </cfRule>
@@ -4048,118 +4120,118 @@
   <sheetFormatPr defaultColWidth="8.515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="C1" s="0" t="s">
+      <c r="A1" s="72" t="s">
         <v>175</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="B1" s="72" t="s">
         <v>176</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="C1" s="72" t="s">
         <v>177</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="D1" s="72" t="s">
         <v>178</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="E1" s="72" t="s">
         <v>179</v>
       </c>
+      <c r="F1" s="72" t="s">
+        <v>180</v>
+      </c>
+      <c r="G1" s="72" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>180</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>181</v>
-      </c>
-      <c r="C2" s="0" t="s">
+      <c r="A2" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="72" t="s">
         <v>183</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="C2" s="72" t="s">
         <v>184</v>
       </c>
-      <c r="F2" s="0" t="n">
+      <c r="D2" s="72" t="s">
+        <v>185</v>
+      </c>
+      <c r="E2" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2" s="72" t="n">
         <v>17</v>
       </c>
-      <c r="G2" s="0" t="s">
-        <v>185</v>
+      <c r="G2" s="72" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="B3" s="76" t="s">
-        <v>187</v>
-      </c>
-      <c r="C3" s="76" t="s">
+      <c r="A3" s="73" t="s">
         <v>188</v>
       </c>
-      <c r="D3" s="76" t="s">
+      <c r="B3" s="73" t="s">
         <v>189</v>
       </c>
-      <c r="E3" s="76" t="s">
+      <c r="C3" s="73" t="s">
         <v>190</v>
       </c>
-      <c r="F3" s="0" t="n">
+      <c r="D3" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="E3" s="73" t="s">
+        <v>192</v>
+      </c>
+      <c r="F3" s="72" t="n">
         <v>14</v>
       </c>
-      <c r="G3" s="76" t="s">
-        <v>191</v>
+      <c r="G3" s="73" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="77" t="s">
-        <v>192</v>
-      </c>
-      <c r="B4" s="77" t="s">
-        <v>193</v>
-      </c>
-      <c r="C4" s="77" t="s">
+      <c r="A4" s="74" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="77" t="s">
+      <c r="B4" s="74" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="77" t="s">
+      <c r="C4" s="74" t="s">
         <v>196</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="D4" s="74" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="74" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="G4" s="77" t="s">
-        <v>197</v>
+      <c r="G4" s="74" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="77" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" s="77" t="s">
-        <v>198</v>
-      </c>
-      <c r="C5" s="77" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="77" t="s">
+      <c r="A5" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="74" t="s">
         <v>200</v>
       </c>
-      <c r="E5" s="77" t="s">
+      <c r="C5" s="74" t="s">
         <v>201</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="D5" s="74" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" s="74" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" s="72" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="77" t="s">
-        <v>202</v>
+      <c r="G5" s="74" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
